--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
@@ -70,9 +70,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="164" formatCode="0%"/>
   </x:numFmts>
   <x:fonts count="1">
     <x:font>
@@ -168,7 +167,7 @@
     <field x="0"/>
   </colFields>
   <dataFields count="1">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -209,7 +208,7 @@
     <field x="4"/>
   </colFields>
   <dataFields count="1">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -248,7 +247,7 @@
     <field x="4"/>
   </rowFields>
   <dataFields count="1">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -287,7 +286,7 @@
     <field x="4"/>
   </colFields>
   <dataFields count="1">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -342,7 +341,7 @@
     <field x="0"/>
   </colFields>
   <dataFields count="1">
-    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="164"/>
+    <dataField name="NumberOfOrdersPercentageOfBearclaw" fld="2" showDataAs="percent" baseField="0" baseItem="2" numFmtId="9"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
